--- a/evidence/s03a/normal/s02a_finance.xlsx
+++ b/evidence/s03a/normal/s02a_finance.xlsx
@@ -87,7 +87,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>6a7e97612fc11d1cf83ac40186ebdf90</t>
+    <t>eaeea6c8278b2bb3177cc8b04c216fe9</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -129,13 +129,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>9daadaddd7fd39d752c64132e6b5cb52</t>
+    <t>ee76dcd88925a6dd4464f1b9e9f22f05</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-27T00:00:27+08:00</t>
+    <t>2026-10-27T00:27:02+08:00</t>
   </si>
   <si>
     <t>precision</t>

--- a/evidence/s03a/normal/s02a_finance.xlsx
+++ b/evidence/s03a/normal/s02a_finance.xlsx
@@ -87,7 +87,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>eaeea6c8278b2bb3177cc8b04c216fe9</t>
+    <t>de557ce5a22824a5164876621cacf7d6</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -129,13 +129,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>ee76dcd88925a6dd4464f1b9e9f22f05</t>
+    <t>6c96a6a7a8fc3f75ebf4fbb0457aa55a</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-27T00:27:02+08:00</t>
+    <t>2026-10-27T00:32:44+08:00</t>
   </si>
   <si>
     <t>precision</t>

--- a/evidence/s03a/normal/s02a_finance.xlsx
+++ b/evidence/s03a/normal/s02a_finance.xlsx
@@ -87,7 +87,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>de557ce5a22824a5164876621cacf7d6</t>
+    <t>4b268a0cdd685495cb9c83f473402005</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -129,13 +129,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>6c96a6a7a8fc3f75ebf4fbb0457aa55a</t>
+    <t>c0b8221076f18633559b6151694d2d3e</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-27T00:32:44+08:00</t>
+    <t>2026-10-27T00:40:39+08:00</t>
   </si>
   <si>
     <t>precision</t>
